--- a/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
+++ b/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TCGAACAGGTGTTCG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TCG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TCG</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;AACAGGTGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.6067572970811675</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>GTGT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>GGTGTTCGG</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TGTTC&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>

--- a/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
+++ b/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.6067572970811675</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -585,6 +600,11 @@
       </c>
       <c r="I4" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
+++ b/20_Threshold_OUTPUT/direct_A0QVY5_Mycobacterium_tuberculosis_H37Rv.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -605,6 +616,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
